--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.69577027999087</v>
+        <v>9.863062670498518</v>
       </c>
       <c r="D2" t="n">
-        <v>55.05124240806324</v>
+        <v>8.945826891310277</v>
       </c>
       <c r="E2" t="n">
-        <v>3.998571422502658</v>
+        <v>0.6497678561566823</v>
       </c>
       <c r="F2" t="n">
-        <v>9.341797367786723</v>
+        <v>1.518042072265343</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.69883639453973</v>
+        <v>9.701060914112706</v>
       </c>
       <c r="D3" t="n">
-        <v>45.07485412540612</v>
+        <v>7.324663795378495</v>
       </c>
       <c r="E3" t="n">
-        <v>3.998571422502658</v>
+        <v>0.6497678561566823</v>
       </c>
       <c r="F3" t="n">
-        <v>9.341797367786723</v>
+        <v>1.518042072265343</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.88471359276669</v>
+        <v>8.918765958824586</v>
       </c>
       <c r="D4" t="n">
-        <v>58.45724933658784</v>
+        <v>9.499303017195524</v>
       </c>
       <c r="E4" t="n">
-        <v>3.998571422502658</v>
+        <v>0.6497678561566823</v>
       </c>
       <c r="F4" t="n">
-        <v>9.341797367786723</v>
+        <v>1.518042072265343</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.72045691793492</v>
+        <v>10.67957424916443</v>
       </c>
       <c r="D5" t="n">
-        <v>69.26676791052486</v>
+        <v>11.25584978546029</v>
       </c>
       <c r="E5" t="n">
-        <v>3.998571422502658</v>
+        <v>0.6497678561566823</v>
       </c>
       <c r="F5" t="n">
-        <v>9.341797367786723</v>
+        <v>1.518042072265343</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.34015273157307</v>
+        <v>10.61777481888062</v>
       </c>
       <c r="D6" t="n">
-        <v>43.84062043356595</v>
+        <v>7.124100820454466</v>
       </c>
       <c r="E6" t="n">
-        <v>3.998571422502658</v>
+        <v>0.6497678561566823</v>
       </c>
       <c r="F6" t="n">
-        <v>9.341797367786723</v>
+        <v>1.518042072265343</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
